--- a/salidas/empresas/CL.xlsx
+++ b/salidas/empresas/CL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>16.99497604370117</v>
+        <v>16.9949836730957</v>
       </c>
       <c r="C2" t="n">
         <v>27.44499969482422</v>
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>17.67923927307129</v>
+        <v>17.67924308776855</v>
       </c>
       <c r="C4" t="n">
         <v>28.54999923706055</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>18.40813446044922</v>
+        <v>18.40814018249512</v>
       </c>
       <c r="C5" t="n">
         <v>29.55999946594238</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>18.78800392150879</v>
+        <v>18.78801155090332</v>
       </c>
       <c r="C6" t="n">
         <v>30.17000007629395</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>18.6510066986084</v>
+        <v>18.6510124206543</v>
       </c>
       <c r="C7" t="n">
         <v>29.95000076293945</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>18.56612396240234</v>
+        <v>18.56612968444824</v>
       </c>
       <c r="C8" t="n">
         <v>29.65999984741211</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>18.73513984680176</v>
+        <v>18.73513221740723</v>
       </c>
       <c r="C9" t="n">
         <v>29.93000030517578</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>19.43622207641602</v>
+        <v>19.43621444702148</v>
       </c>
       <c r="C10" t="n">
         <v>31.04999923706055</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>20.12844276428223</v>
+        <v>20.12843704223633</v>
       </c>
       <c r="C11" t="n">
         <v>31.98500061035156</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>20.46825981140137</v>
+        <v>20.46826171875</v>
       </c>
       <c r="C12" t="n">
         <v>32.52500152587891</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>20.52804565429688</v>
+        <v>20.52805328369141</v>
       </c>
       <c r="C13" t="n">
         <v>32.61999893188477</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>21.5950927734375</v>
+        <v>21.59508514404297</v>
       </c>
       <c r="C14" t="n">
         <v>34.15000152587891</v>
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>21.11766052246094</v>
+        <v>21.11765289306641</v>
       </c>
       <c r="C16" t="n">
         <v>33.39500045776367</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>21.53373908996582</v>
+        <v>21.53374481201172</v>
       </c>
       <c r="C17" t="n">
         <v>33.86999893188477</v>
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>21.09268569946289</v>
+        <v>21.09268188476562</v>
       </c>
       <c r="C20" t="n">
         <v>33</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>21.19495964050293</v>
+        <v>21.19496536254883</v>
       </c>
       <c r="C21" t="n">
         <v>33.15999984741211</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>22.79288291931152</v>
+        <v>22.79288673400879</v>
       </c>
       <c r="C22" t="n">
         <v>35.65999984741211</v>
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>25.71892356872559</v>
+        <v>25.71892738342285</v>
       </c>
       <c r="C24" t="n">
         <v>40.04000091552734</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>25.03806495666504</v>
+        <v>25.03805541992188</v>
       </c>
       <c r="C25" t="n">
         <v>38.97999954223633</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>24.68773651123047</v>
+        <v>24.68773460388184</v>
       </c>
       <c r="C26" t="n">
         <v>38.25</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>24.55541610717773</v>
+        <v>24.55542755126953</v>
       </c>
       <c r="C27" t="n">
         <v>38.04499816894531</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>25.14276695251465</v>
+        <v>25.14277648925781</v>
       </c>
       <c r="C28" t="n">
         <v>38.95500183105469</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>22.93441581726074</v>
+        <v>22.93441963195801</v>
       </c>
       <c r="C29" t="n">
         <v>35.34999847412109</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>24.12167549133301</v>
+        <v>24.12168312072754</v>
       </c>
       <c r="C30" t="n">
         <v>37.18000030517578</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>22.41539573669434</v>
+        <v>22.41539001464844</v>
       </c>
       <c r="C31" t="n">
         <v>34.54999923706055</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>24.23382186889648</v>
+        <v>24.23381233215332</v>
       </c>
       <c r="C32" t="n">
         <v>37.1349983215332</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>24.80809211730957</v>
+        <v>24.8080940246582</v>
       </c>
       <c r="C33" t="n">
         <v>38.01499938964844</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>24.58621215820312</v>
+        <v>24.58620834350586</v>
       </c>
       <c r="C34" t="n">
         <v>37.67499923706055</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>20.60928344726562</v>
+        <v>20.60927963256836</v>
       </c>
       <c r="C35" t="n">
         <v>31.3799991607666</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>21.36784172058105</v>
+        <v>21.36785125732422</v>
       </c>
       <c r="C36" t="n">
         <v>32.53499984741211</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>22.5073356628418</v>
+        <v>22.50733757019043</v>
       </c>
       <c r="C37" t="n">
         <v>34.27000045776367</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>21.49353981018066</v>
+        <v>21.49353408813477</v>
       </c>
       <c r="C38" t="n">
         <v>32.52000045776367</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>19.88747406005859</v>
+        <v>19.88747024536133</v>
       </c>
       <c r="C39" t="n">
         <v>30.09000015258789</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>19.49090576171875</v>
+        <v>19.49091148376465</v>
       </c>
       <c r="C40" t="n">
         <v>29.48999977111816</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>19.64011383056641</v>
+        <v>19.6401195526123</v>
       </c>
       <c r="C41" t="n">
         <v>29.5</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>21.95367050170898</v>
+        <v>21.95366668701172</v>
       </c>
       <c r="C42" t="n">
         <v>32.97499847412109</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>23.54817008972168</v>
+        <v>23.54816627502441</v>
       </c>
       <c r="C43" t="n">
         <v>35.36999893188477</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>24.25870895385742</v>
+        <v>24.25870132446289</v>
       </c>
       <c r="C44" t="n">
         <v>36.22000122070312</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>24.34577178955078</v>
+        <v>24.34577560424805</v>
       </c>
       <c r="C45" t="n">
         <v>36.34999847412109</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>25.54464721679688</v>
+        <v>25.54464912414551</v>
       </c>
       <c r="C46" t="n">
         <v>38.13999938964844</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>26.47924423217773</v>
+        <v>26.47924041748047</v>
       </c>
       <c r="C47" t="n">
         <v>39.31499862670898</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>28.35161972045898</v>
+        <v>28.35161781311035</v>
       </c>
       <c r="C48" t="n">
         <v>42.09500122070312</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>27.66462326049805</v>
+        <v>27.66463088989258</v>
       </c>
       <c r="C49" t="n">
         <v>41.07500076293945</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>27.10124206542969</v>
+        <v>27.10124015808105</v>
       </c>
       <c r="C50" t="n">
         <v>40.01499938964844</v>
@@ -1455,7 +1467,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>28.87233924865723</v>
+        <v>28.87232208251953</v>
       </c>
       <c r="C52" t="n">
         <v>42.63000106811523</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>28.65882682800293</v>
+        <v>28.65883445739746</v>
       </c>
       <c r="C53" t="n">
         <v>42.04999923706055</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>26.61080360412598</v>
+        <v>26.61079788208008</v>
       </c>
       <c r="C54" t="n">
         <v>39.04499816894531</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>26.83911323547363</v>
+        <v>26.8391170501709</v>
       </c>
       <c r="C55" t="n">
         <v>39.38000106811523</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>27.08699417114258</v>
+        <v>27.08699035644531</v>
       </c>
       <c r="C56" t="n">
         <v>39.4900016784668</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>25.32417869567871</v>
+        <v>25.32416915893555</v>
       </c>
       <c r="C57" t="n">
         <v>36.91999816894531</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>26.35990905761719</v>
+        <v>26.35991477966309</v>
       </c>
       <c r="C58" t="n">
         <v>38.43000030517578</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>26.6319637298584</v>
+        <v>26.63196754455566</v>
       </c>
       <c r="C59" t="n">
         <v>38.56000137329102</v>
@@ -1680,7 +1692,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>27.75429534912109</v>
+        <v>27.75429725646973</v>
       </c>
       <c r="C61" t="n">
         <v>40.18500137329102</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>26.69018936157227</v>
+        <v>26.69017791748047</v>
       </c>
       <c r="C62" t="n">
         <v>38.3849983215332</v>
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>27.29859352111816</v>
+        <v>27.2985954284668</v>
       </c>
       <c r="C63" t="n">
         <v>39.2599983215332</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>28.07736968994141</v>
+        <v>28.07737731933594</v>
       </c>
       <c r="C64" t="n">
         <v>40.38000106811523</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>29.53627586364746</v>
+        <v>29.5362720489502</v>
       </c>
       <c r="C65" t="n">
         <v>42.17499923706055</v>
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>30.64980125427246</v>
+        <v>30.6497859954834</v>
       </c>
       <c r="C66" t="n">
         <v>43.76499938964844</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>30.6077766418457</v>
+        <v>30.6077709197998</v>
       </c>
       <c r="C67" t="n">
         <v>43.70500183105469</v>
@@ -1900,7 +1912,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1929,11 +1941,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>31.71083641052246</v>
+        <v>31.71083068847656</v>
       </c>
       <c r="C69" t="n">
         <v>44.98500061035156</v>
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>31.25616836547852</v>
+        <v>31.25618934631348</v>
       </c>
       <c r="C70" t="n">
         <v>44.34000015258789</v>
@@ -1987,7 +1999,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2016,11 +2028,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>32.45556640625</v>
+        <v>32.45556259155273</v>
       </c>
       <c r="C72" t="n">
         <v>45.75</v>
@@ -2045,11 +2057,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>32.77126312255859</v>
+        <v>32.77125930786133</v>
       </c>
       <c r="C73" t="n">
         <v>46.19499969482422</v>
@@ -2074,11 +2086,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>32.38768768310547</v>
+        <v>32.38769149780273</v>
       </c>
       <c r="C74" t="n">
         <v>45.36000061035156</v>
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>33.26591491699219</v>
+        <v>33.26591873168945</v>
       </c>
       <c r="C75" t="n">
         <v>46.59000015258789</v>
@@ -2132,11 +2144,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>34.90814971923828</v>
+        <v>34.90816116333008</v>
       </c>
       <c r="C76" t="n">
         <v>48.88999938964844</v>
@@ -2161,7 +2173,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>35.31682968139648</v>
+        <v>35.31682205200195</v>
       </c>
       <c r="C78" t="n">
         <v>49.15000152587891</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>37.40062713623047</v>
+        <v>37.4006233215332</v>
       </c>
       <c r="C79" t="n">
         <v>52.04999923706055</v>
@@ -2248,7 +2260,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>38.42016220092773</v>
+        <v>38.42015838623047</v>
       </c>
       <c r="C81" t="n">
         <v>53.15499877929688</v>
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>38.7490234375</v>
+        <v>38.74902725219727</v>
       </c>
       <c r="C82" t="n">
         <v>53.61000061035156</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>38.14608383178711</v>
+        <v>38.14606475830078</v>
       </c>
       <c r="C83" t="n">
         <v>52.47999954223633</v>
@@ -2364,11 +2376,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>39.4326171875</v>
+        <v>39.4326286315918</v>
       </c>
       <c r="C84" t="n">
         <v>54.25</v>
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>37.99342727661133</v>
+        <v>37.99341583251953</v>
       </c>
       <c r="C85" t="n">
         <v>52.27000045776367</v>
@@ -2422,11 +2434,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>39.24515533447266</v>
+        <v>39.24514770507812</v>
       </c>
       <c r="C86" t="n">
         <v>53.68500137329102</v>
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>41.82566452026367</v>
+        <v>41.82567977905273</v>
       </c>
       <c r="C87" t="n">
         <v>57.21500015258789</v>
@@ -2480,11 +2492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>43.14152526855469</v>
+        <v>43.14152908325195</v>
       </c>
       <c r="C88" t="n">
         <v>59.01499938964844</v>
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>43.89768981933594</v>
+        <v>43.89768218994141</v>
       </c>
       <c r="C89" t="n">
         <v>59.70500183105469</v>
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>42.52646636962891</v>
+        <v>42.52645874023438</v>
       </c>
       <c r="C90" t="n">
         <v>57.84000015258789</v>
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>42.1220703125</v>
+        <v>42.12207794189453</v>
       </c>
       <c r="C91" t="n">
         <v>57.29000091552734</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>44.27500915527344</v>
+        <v>44.27501678466797</v>
       </c>
       <c r="C92" t="n">
         <v>59.86999893188477</v>
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>42.72201919555664</v>
+        <v>42.72201538085938</v>
       </c>
       <c r="C93" t="n">
         <v>57.77000045776367</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>43.85348892211914</v>
+        <v>43.85348510742188</v>
       </c>
       <c r="C94" t="n">
         <v>59.29999923706055</v>
@@ -2683,11 +2695,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>48.12712478637695</v>
+        <v>48.12714004516602</v>
       </c>
       <c r="C95" t="n">
         <v>64.73000335693359</v>
@@ -2712,11 +2724,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>48.93010330200195</v>
+        <v>48.93010711669922</v>
       </c>
       <c r="C96" t="n">
         <v>65.80999755859375</v>
@@ -2741,11 +2753,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>48.48401260375977</v>
+        <v>48.48401641845703</v>
       </c>
       <c r="C97" t="n">
         <v>65.20999908447266</v>
@@ -2770,11 +2782,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>45.76522064208984</v>
+        <v>45.76520919799805</v>
       </c>
       <c r="C98" t="n">
         <v>61.22999954223633</v>
@@ -2799,11 +2811,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>46.96109390258789</v>
+        <v>46.96109771728516</v>
       </c>
       <c r="C99" t="n">
         <v>62.83000183105469</v>
@@ -2828,11 +2840,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>48.48584365844727</v>
+        <v>48.48585510253906</v>
       </c>
       <c r="C100" t="n">
         <v>64.87000274658203</v>
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>50.57311248779297</v>
+        <v>50.57314682006836</v>
       </c>
       <c r="C101" t="n">
         <v>67.30000305175781</v>
@@ -2886,11 +2898,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>51.39972686767578</v>
+        <v>51.39973449707031</v>
       </c>
       <c r="C102" t="n">
         <v>68.40000152587891</v>
@@ -2915,11 +2927,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>51.23440933227539</v>
+        <v>51.23440170288086</v>
       </c>
       <c r="C103" t="n">
         <v>68.18000030517578</v>
@@ -2944,7 +2956,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2973,7 +2985,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -3002,11 +3014,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>49.26469039916992</v>
+        <v>49.26469421386719</v>
       </c>
       <c r="C106" t="n">
         <v>65.22000122070312</v>
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>50.80252838134766</v>
+        <v>50.80253601074219</v>
       </c>
       <c r="C107" t="n">
         <v>66.87999725341797</v>
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>52.86108779907227</v>
+        <v>52.86106872558594</v>
       </c>
       <c r="C108" t="n">
         <v>69.58999633789062</v>
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>52.55722427368164</v>
+        <v>52.55723190307617</v>
       </c>
       <c r="C109" t="n">
         <v>69.19000244140625</v>
@@ -3118,11 +3130,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>51.55784225463867</v>
+        <v>51.55783843994141</v>
       </c>
       <c r="C110" t="n">
         <v>67.51999664306641</v>
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>54.07769775390625</v>
+        <v>54.07770538330078</v>
       </c>
       <c r="C111" t="n">
         <v>70.81999969482422</v>
@@ -3176,11 +3188,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>52.94756317138672</v>
+        <v>52.94756698608398</v>
       </c>
       <c r="C112" t="n">
         <v>69.33999633789062</v>
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>51.66131973266602</v>
+        <v>51.66133499145508</v>
       </c>
       <c r="C113" t="n">
         <v>67.27999877929688</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>51.28507995605469</v>
+        <v>51.28508377075195</v>
       </c>
       <c r="C114" t="n">
         <v>66.79000091552734</v>
@@ -3263,11 +3275,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>50.22545623779297</v>
+        <v>50.22544860839844</v>
       </c>
       <c r="C115" t="n">
         <v>65.41000366210938</v>
@@ -3292,11 +3304,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>52.52392578125</v>
+        <v>52.52392196655273</v>
       </c>
       <c r="C116" t="n">
         <v>68.01999664306641</v>
@@ -3321,11 +3333,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>48.50085830688477</v>
+        <v>48.50086212158203</v>
       </c>
       <c r="C117" t="n">
         <v>62.81000137329102</v>
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>49.00276184082031</v>
+        <v>49.00275802612305</v>
       </c>
       <c r="C118" t="n">
         <v>63.45999908447266</v>
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>51.52636337280273</v>
+        <v>51.5263671875</v>
       </c>
       <c r="C119" t="n">
         <v>66.34999847412109</v>
@@ -3408,11 +3420,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>51.00604248046875</v>
+        <v>51.00603866577148</v>
       </c>
       <c r="C120" t="n">
         <v>65.68000030517578</v>
@@ -3437,7 +3449,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3466,11 +3478,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>52.7637939453125</v>
+        <v>52.7637825012207</v>
       </c>
       <c r="C122" t="n">
         <v>67.52999877929688</v>
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>51.28705978393555</v>
+        <v>51.28706359863281</v>
       </c>
       <c r="C123" t="n">
         <v>65.63999938964844</v>
@@ -3524,11 +3536,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>55.20156860351562</v>
+        <v>55.2015495300293</v>
       </c>
       <c r="C124" t="n">
         <v>70.65000152587891</v>
@@ -3553,11 +3565,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>55.71575164794922</v>
+        <v>55.71574401855469</v>
       </c>
       <c r="C125" t="n">
         <v>70.91999816894531</v>
@@ -3582,11 +3594,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>55.31509399414062</v>
+        <v>55.31508636474609</v>
       </c>
       <c r="C126" t="n">
         <v>70.41000366210938</v>
@@ -3611,11 +3623,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>57.50694274902344</v>
+        <v>57.5069465637207</v>
       </c>
       <c r="C127" t="n">
         <v>73.19999694824219</v>
@@ -3640,11 +3652,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>58.78070449829102</v>
+        <v>58.78071212768555</v>
       </c>
       <c r="C128" t="n">
         <v>74.43000030517578</v>
@@ -3669,11 +3681,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>58.70965194702148</v>
+        <v>58.70964431762695</v>
       </c>
       <c r="C129" t="n">
         <v>74.33999633789062</v>
@@ -3698,11 +3710,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>58.55170822143555</v>
+        <v>58.55168151855469</v>
       </c>
       <c r="C130" t="n">
         <v>74.13999938964844</v>
@@ -3727,11 +3739,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>56.66441345214844</v>
+        <v>56.66440200805664</v>
       </c>
       <c r="C131" t="n">
         <v>71.36000061035156</v>
@@ -3756,11 +3768,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>51.79681015014648</v>
+        <v>51.79680252075195</v>
       </c>
       <c r="C132" t="n">
         <v>65.23000335693359</v>
@@ -3785,11 +3797,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>51.96354675292969</v>
+        <v>51.96355819702148</v>
       </c>
       <c r="C133" t="n">
         <v>65.44000244140625</v>
@@ -3814,11 +3826,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>51.57707977294922</v>
+        <v>51.57708740234375</v>
       </c>
       <c r="C134" t="n">
         <v>64.58000183105469</v>
@@ -3843,7 +3855,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3872,11 +3884,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>58.45351409912109</v>
+        <v>58.4534912109375</v>
       </c>
       <c r="C136" t="n">
         <v>73.19000244140625</v>
@@ -3901,11 +3913,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>57.84619140625</v>
+        <v>57.84616470336914</v>
       </c>
       <c r="C137" t="n">
         <v>72.04000091552734</v>
@@ -3930,11 +3942,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>61.31500625610352</v>
+        <v>61.31498718261719</v>
       </c>
       <c r="C138" t="n">
         <v>76.36000061035156</v>
@@ -3959,11 +3971,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>59.52438735961914</v>
+        <v>59.52437973022461</v>
       </c>
       <c r="C139" t="n">
         <v>74.12999725341797</v>
@@ -3988,11 +4000,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>58.2974967956543</v>
+        <v>58.29747772216797</v>
       </c>
       <c r="C140" t="n">
         <v>72.19999694824219</v>
@@ -4017,11 +4029,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>57.84532928466797</v>
+        <v>57.84530639648438</v>
       </c>
       <c r="C141" t="n">
         <v>71.63999938964844</v>
@@ -4046,11 +4058,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>58.82231521606445</v>
+        <v>58.82230377197266</v>
       </c>
       <c r="C142" t="n">
         <v>72.84999847412109</v>
@@ -4075,11 +4087,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>57.197265625</v>
+        <v>57.19726943969727</v>
       </c>
       <c r="C143" t="n">
         <v>70.44999694824219</v>
@@ -4104,11 +4116,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>58.82101440429688</v>
+        <v>58.82101058959961</v>
       </c>
       <c r="C144" t="n">
         <v>72.44999694824219</v>
@@ -4133,11 +4145,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>61.2567024230957</v>
+        <v>61.25668334960938</v>
       </c>
       <c r="C145" t="n">
         <v>75.44999694824219</v>
@@ -4162,11 +4174,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>60.58701324462891</v>
+        <v>60.58701705932617</v>
       </c>
       <c r="C146" t="n">
         <v>74.23999786376953</v>
@@ -4191,11 +4203,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>56.28619384765625</v>
+        <v>56.28620529174805</v>
       </c>
       <c r="C147" t="n">
         <v>68.97000122070312</v>
@@ -4220,11 +4232,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>58.49781036376953</v>
+        <v>58.4978141784668</v>
       </c>
       <c r="C148" t="n">
         <v>71.68000030517578</v>
@@ -4249,11 +4261,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>53.54600143432617</v>
+        <v>53.54598617553711</v>
       </c>
       <c r="C149" t="n">
         <v>65.23000335693359</v>
@@ -4278,11 +4290,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>51.78931045532227</v>
+        <v>51.789306640625</v>
       </c>
       <c r="C150" t="n">
         <v>63.09000015258789</v>
@@ -4307,11 +4319,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>53.20121765136719</v>
+        <v>53.20122146606445</v>
       </c>
       <c r="C151" t="n">
         <v>64.80999755859375</v>
@@ -4336,11 +4348,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>55.36149215698242</v>
+        <v>55.36150741577148</v>
       </c>
       <c r="C152" t="n">
         <v>67.01000213623047</v>
@@ -4365,11 +4377,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>54.86579132080078</v>
+        <v>54.86578750610352</v>
       </c>
       <c r="C153" t="n">
         <v>66.41000366210938</v>
@@ -4394,11 +4406,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>55.31192779541016</v>
+        <v>55.31191253662109</v>
       </c>
       <c r="C154" t="n">
         <v>66.94999694824219</v>
@@ -4423,11 +4435,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>49.52559280395508</v>
+        <v>49.52559661865234</v>
       </c>
       <c r="C155" t="n">
         <v>59.54999923706055</v>
@@ -4452,11 +4464,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>52.82730484008789</v>
+        <v>52.82728958129883</v>
       </c>
       <c r="C156" t="n">
         <v>63.52000045776367</v>
@@ -4481,11 +4493,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>49.50065231323242</v>
+        <v>49.50064849853516</v>
       </c>
       <c r="C157" t="n">
         <v>59.52000045776367</v>
@@ -4510,11 +4522,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>54.15520095825195</v>
+        <v>54.15520858764648</v>
       </c>
       <c r="C158" t="n">
         <v>64.68000030517578</v>
@@ -4539,11 +4551,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>55.15156173706055</v>
+        <v>55.15156936645508</v>
       </c>
       <c r="C159" t="n">
         <v>65.87000274658203</v>
@@ -4568,11 +4580,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>57.38710784912109</v>
+        <v>57.3870964050293</v>
       </c>
       <c r="C160" t="n">
         <v>68.54000091552734</v>
@@ -4597,11 +4609,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>61.32752227783203</v>
+        <v>61.32749557495117</v>
       </c>
       <c r="C161" t="n">
         <v>72.79000091552734</v>
@@ -4626,7 +4638,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4655,11 +4667,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>60.38388061523438</v>
+        <v>60.38385009765625</v>
       </c>
       <c r="C163" t="n">
         <v>71.66999816894531</v>
@@ -4684,11 +4696,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>60.79372024536133</v>
+        <v>60.79373168945312</v>
       </c>
       <c r="C164" t="n">
         <v>71.73999786376953</v>
@@ -4713,11 +4725,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>62.83601379394531</v>
+        <v>62.83601760864258</v>
       </c>
       <c r="C165" t="n">
         <v>74.15000152587891</v>
@@ -4742,11 +4754,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>62.2936897277832</v>
+        <v>62.29368591308594</v>
       </c>
       <c r="C166" t="n">
         <v>73.51000213623047</v>
@@ -4771,11 +4783,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>58.50116348266602</v>
+        <v>58.50115203857422</v>
       </c>
       <c r="C167" t="n">
         <v>68.59999847412109</v>
@@ -4800,11 +4812,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>57.83597946166992</v>
+        <v>57.83597564697266</v>
       </c>
       <c r="C168" t="n">
         <v>67.81999969482422</v>
@@ -4829,11 +4841,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>58.7057991027832</v>
+        <v>58.7058219909668</v>
       </c>
       <c r="C169" t="n">
         <v>68.83999633789062</v>
@@ -4858,11 +4870,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>63.30038452148438</v>
+        <v>63.30039978027344</v>
       </c>
       <c r="C170" t="n">
         <v>73.77999877929688</v>
@@ -4887,11 +4899,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>57.97246170043945</v>
+        <v>57.97245788574219</v>
       </c>
       <c r="C171" t="n">
         <v>67.56999969482422</v>
@@ -4916,11 +4928,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>56.93431854248047</v>
+        <v>56.93431091308594</v>
       </c>
       <c r="C172" t="n">
         <v>66.36000061035156</v>
@@ -4945,11 +4957,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>60.65533447265625</v>
+        <v>60.65534591674805</v>
       </c>
       <c r="C173" t="n">
         <v>70.26999664306641</v>
@@ -4974,11 +4986,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>62.43350219726562</v>
+        <v>62.4334831237793</v>
       </c>
       <c r="C174" t="n">
         <v>72.33000183105469</v>
@@ -5003,11 +5015,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>63.23623657226562</v>
+        <v>63.23624801635742</v>
       </c>
       <c r="C175" t="n">
         <v>73.26000213623047</v>
@@ -5032,11 +5044,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>67.03050231933594</v>
+        <v>67.03050994873047</v>
       </c>
       <c r="C176" t="n">
         <v>77.19999694824219</v>
@@ -5061,11 +5073,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>68.81913757324219</v>
+        <v>68.81914520263672</v>
       </c>
       <c r="C177" t="n">
         <v>79.26000213623047</v>
@@ -5090,11 +5102,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>66.98708343505859</v>
+        <v>66.98709106445312</v>
       </c>
       <c r="C178" t="n">
         <v>77.15000152587891</v>
@@ -5119,7 +5131,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5148,11 +5160,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>74.76893615722656</v>
+        <v>74.76891326904297</v>
       </c>
       <c r="C180" t="n">
         <v>85.63999938964844</v>
@@ -5177,11 +5189,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>74.65540313720703</v>
+        <v>74.65543365478516</v>
       </c>
       <c r="C181" t="n">
         <v>85.51000213623047</v>
@@ -5206,7 +5218,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5235,11 +5247,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>66.02056121826172</v>
+        <v>66.02057647705078</v>
       </c>
       <c r="C183" t="n">
         <v>75.19999694824219</v>
@@ -5264,11 +5276,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>69.20746612548828</v>
+        <v>69.20747375488281</v>
       </c>
       <c r="C184" t="n">
         <v>78.83000183105469</v>
@@ -5293,7 +5305,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5322,11 +5334,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>73.96739959716797</v>
+        <v>73.96738433837891</v>
       </c>
       <c r="C186" t="n">
         <v>83.77999877929688</v>
@@ -5351,7 +5363,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5380,11 +5392,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>70.56687164306641</v>
+        <v>70.56684875488281</v>
       </c>
       <c r="C188" t="n">
         <v>79.5</v>
@@ -5409,11 +5421,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>69.19103240966797</v>
+        <v>69.19100952148438</v>
       </c>
       <c r="C189" t="n">
         <v>77.94999694824219</v>
@@ -5438,11 +5450,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>67.08734130859375</v>
+        <v>67.08733367919922</v>
       </c>
       <c r="C190" t="n">
         <v>75.58000183105469</v>
@@ -5467,11 +5479,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>68.0382080078125</v>
+        <v>68.03821563720703</v>
       </c>
       <c r="C191" t="n">
         <v>76.19000244140625</v>
@@ -5496,11 +5508,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>66.99340057373047</v>
+        <v>66.99339294433594</v>
       </c>
       <c r="C192" t="n">
         <v>75.01999664306641</v>
@@ -5525,7 +5537,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5554,11 +5566,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>74.02838134765625</v>
+        <v>74.02838897705078</v>
       </c>
       <c r="C194" t="n">
         <v>82.44999694824219</v>
@@ -5583,11 +5595,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>69.09017181396484</v>
+        <v>69.09018707275391</v>
       </c>
       <c r="C195" t="n">
         <v>76.94999694824219</v>
@@ -5612,11 +5624,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>68.08457183837891</v>
+        <v>68.08458709716797</v>
       </c>
       <c r="C196" t="n">
         <v>75.83000183105469</v>
@@ -5641,11 +5653,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>69.585693359375</v>
+        <v>69.58568572998047</v>
       </c>
       <c r="C197" t="n">
         <v>77.05000305175781</v>
@@ -5670,7 +5682,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5699,7 +5711,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5728,11 +5740,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>71.54567718505859</v>
+        <v>71.54568481445312</v>
       </c>
       <c r="C200" t="n">
         <v>78.73999786376953</v>
@@ -5757,11 +5769,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>71.06410980224609</v>
+        <v>71.06409454345703</v>
       </c>
       <c r="C201" t="n">
         <v>78.20999908447266</v>
@@ -5786,11 +5798,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>63.83141326904297</v>
+        <v>63.83140563964844</v>
       </c>
       <c r="C202" t="n">
         <v>70.25</v>
@@ -5815,7 +5827,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5844,7 +5856,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5873,11 +5885,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>72.06316375732422</v>
+        <v>72.06317901611328</v>
       </c>
       <c r="C205" t="n">
         <v>78.79000091552734</v>
@@ -5902,7 +5914,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5931,11 +5943,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>67.46355438232422</v>
+        <v>67.46353912353516</v>
       </c>
       <c r="C207" t="n">
         <v>73.30000305175781</v>
@@ -5960,11 +5972,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>69.16622924804688</v>
+        <v>69.16623687744141</v>
       </c>
       <c r="C208" t="n">
         <v>75.15000152587891</v>
@@ -5989,11 +6001,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>73.91535949707031</v>
+        <v>73.91535186767578</v>
       </c>
       <c r="C209" t="n">
         <v>79.80000305175781</v>
@@ -6018,11 +6030,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>68.89502716064453</v>
+        <v>68.89501953125</v>
       </c>
       <c r="C210" t="n">
         <v>74.37999725341797</v>
@@ -6047,7 +6059,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6076,11 +6088,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>71.08287811279297</v>
+        <v>71.08287048339844</v>
       </c>
       <c r="C212" t="n">
         <v>76.26000213623047</v>
@@ -6105,11 +6117,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>68.48228454589844</v>
+        <v>68.48226928710938</v>
       </c>
       <c r="C213" t="n">
         <v>73.47000122070312</v>
@@ -6134,11 +6146,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>66.28250122070312</v>
+        <v>66.28249359130859</v>
       </c>
       <c r="C214" t="n">
         <v>71.11000061035156</v>
@@ -6163,11 +6175,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>70.48252105712891</v>
+        <v>70.48251342773438</v>
       </c>
       <c r="C215" t="n">
         <v>75.12000274658203</v>
@@ -6192,11 +6204,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>73.90718078613281</v>
+        <v>73.90716552734375</v>
       </c>
       <c r="C216" t="n">
         <v>78.76999664306641</v>
@@ -6221,11 +6233,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>74.78913879394531</v>
+        <v>74.78914642333984</v>
       </c>
       <c r="C217" t="n">
         <v>79.70999908447266</v>
@@ -6250,7 +6262,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6279,11 +6291,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>81.66368103027344</v>
+        <v>81.66368865966797</v>
       </c>
       <c r="C219" t="n">
         <v>86.51999664306641</v>
@@ -6308,11 +6320,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>84.99555969238281</v>
+        <v>84.99556732177734</v>
       </c>
       <c r="C220" t="n">
         <v>90.05000305175781</v>
@@ -6337,7 +6349,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6366,7 +6378,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6395,7 +6407,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6424,11 +6436,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>94.64590454101562</v>
+        <v>94.64591217041016</v>
       </c>
       <c r="C224" t="n">
         <v>99.19000244140625</v>
@@ -6453,7 +6465,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6482,7 +6494,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6511,11 +6523,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>89.86391448974609</v>
+        <v>89.86392211914062</v>
       </c>
       <c r="C227" t="n">
         <v>93.70999908447266</v>
@@ -6540,11 +6552,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>92.66407012939453</v>
+        <v>92.66405487060547</v>
       </c>
       <c r="C228" t="n">
         <v>96.62999725341797</v>
@@ -6569,11 +6581,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>87.1788330078125</v>
+        <v>87.17881774902344</v>
       </c>
       <c r="C229" t="n">
         <v>90.91000366210938</v>
@@ -6598,7 +6610,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6627,11 +6639,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>87.92383575439453</v>
+        <v>87.923828125</v>
       </c>
       <c r="C231" t="n">
         <v>91.16999816894531</v>
@@ -6656,11 +6668,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>90.36375427246094</v>
+        <v>90.36374664306641</v>
       </c>
       <c r="C232" t="n">
         <v>93.69999694824219</v>
@@ -6685,7 +6697,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6714,7 +6726,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6743,11 +6755,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>88.15377044677734</v>
+        <v>88.15376281738281</v>
       </c>
       <c r="C235" t="n">
         <v>90.90000152587891</v>
@@ -6772,7 +6784,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6801,11 +6813,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>82.01899719238281</v>
+        <v>82.01898956298828</v>
       </c>
       <c r="C237" t="n">
         <v>84.06999969482422</v>
@@ -6830,11 +6842,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>77.98975372314453</v>
+        <v>77.98976135253906</v>
       </c>
       <c r="C238" t="n">
         <v>79.94000244140625</v>
@@ -6859,7 +6871,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6888,11 +6900,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>78.95459747314453</v>
+        <v>78.95460510253906</v>
       </c>
       <c r="C240" t="n">
         <v>80.38999938964844</v>
@@ -6917,11 +6929,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>77.60905456542969</v>
+        <v>77.60906219482422</v>
       </c>
       <c r="C241" t="n">
         <v>79.01999664306641</v>
@@ -6946,7 +6958,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6975,11 +6987,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>97.96604919433594</v>
+        <v>97.96604156494141</v>
       </c>
       <c r="C243" t="n">
         <v>99.13999938964844</v>
@@ -7004,7 +7016,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7033,7 +7045,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7062,7 +7074,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7091,7 +7103,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7120,7 +7132,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7149,7 +7161,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7178,32 +7190,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>85.93000030517578</v>
+        <v>85.31999969482422</v>
       </c>
       <c r="C250" t="n">
-        <v>85.93000030517578</v>
+        <v>85.31999969482422</v>
       </c>
       <c r="D250" t="n">
-        <v>90083700</v>
+        <v>94862200</v>
       </c>
       <c r="E250" t="n">
         <v>2.53</v>
       </c>
       <c r="F250" t="n">
-        <v>33.96442699809319</v>
+        <v>33.72332003747992</v>
       </c>
       <c r="G250" t="n">
         <v>797172829</v>
       </c>
       <c r="H250" t="n">
-        <v>68501061439.24784</v>
+        <v>68014785527.00216</v>
       </c>
       <c r="I250" t="n">
-        <v>0.113003976958176</v>
+        <v>0.1189982856277205</v>
       </c>
     </row>
   </sheetData>
@@ -7235,75 +7247,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40024</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7339,13 +7351,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7381,13 +7393,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40297</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7423,13 +7435,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40024</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7465,13 +7477,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7507,13 +7519,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7540,7 +7552,7 @@
       <c r="I7" t="n">
         <v>2.185</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K7" t="n">
@@ -7553,13 +7565,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40297</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7586,7 +7598,7 @@
       <c r="I8" t="n">
         <v>2.045</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K8" t="n">
@@ -7599,13 +7611,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40388</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7632,7 +7644,7 @@
       <c r="I9" t="n">
         <v>2.095</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K9" t="n">
@@ -7645,13 +7657,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40479</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7678,7 +7690,7 @@
       <c r="I10" t="n">
         <v>2.14</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K10" t="n">
@@ -7691,13 +7703,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7724,7 +7736,7 @@
       <c r="I11" t="n">
         <v>2.155</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="K11" t="n">
@@ -7737,13 +7749,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40661</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7770,7 +7782,7 @@
       <c r="I12" t="n">
         <v>2.39</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40661</v>
       </c>
       <c r="K12" t="n">
@@ -7783,13 +7795,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7816,7 +7828,7 @@
       <c r="I13" t="n">
         <v>2.435</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="K13" t="n">
@@ -7829,13 +7841,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7862,7 +7874,7 @@
       <c r="I14" t="n">
         <v>2.485</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="K14" t="n">
@@ -7875,13 +7887,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7908,7 +7920,7 @@
       <c r="I15" t="n">
         <v>2.47</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="K15" t="n">
@@ -7921,13 +7933,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7954,7 +7966,7 @@
       <c r="I16" t="n">
         <v>2.505</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="K16" t="n">
@@ -7967,13 +7979,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8000,7 +8012,7 @@
       <c r="I17" t="n">
         <v>2.525</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="K17" t="n">
@@ -8013,13 +8025,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8046,7 +8058,7 @@
       <c r="I18" t="n">
         <v>2.55</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="K18" t="n">
@@ -8059,13 +8071,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8092,7 +8104,7 @@
       <c r="I19" t="n">
         <v>2.575</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="K19" t="n">
@@ -8105,13 +8117,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8138,7 +8150,7 @@
       <c r="I20" t="n">
         <v>2.445</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="K20" t="n">
@@ -8151,13 +8163,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8184,7 +8196,7 @@
       <c r="I21" t="n">
         <v>2.395</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="K21" t="n">
@@ -8197,13 +8209,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8230,7 +8242,7 @@
       <c r="I22" t="n">
         <v>2.415</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="K22" t="n">
@@ -8243,13 +8255,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8276,7 +8288,7 @@
       <c r="I23" t="n">
         <v>2.385</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="K23" t="n">
@@ -8289,13 +8301,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8322,7 +8334,7 @@
       <c r="I24" t="n">
         <v>2.32</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="K24" t="n">
@@ -8335,13 +8347,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8368,7 +8380,7 @@
       <c r="I25" t="n">
         <v>2.39</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K25" t="n">
@@ -8381,13 +8393,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8414,7 +8426,7 @@
       <c r="I26" t="n">
         <v>2.28</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="K26" t="n">
@@ -8427,13 +8439,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8460,7 +8472,7 @@
       <c r="I27" t="n">
         <v>2.36</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="K27" t="n">
@@ -8473,13 +8485,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8506,7 +8518,7 @@
       <c r="I28" t="n">
         <v>2.53</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="K28" t="n">
@@ -8519,13 +8531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8552,7 +8564,7 @@
       <c r="I29" t="n">
         <v>2.49</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="K29" t="n">
@@ -8565,13 +8577,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8598,7 +8610,7 @@
       <c r="I30" t="n">
         <v>2.7</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K30" t="n">
@@ -8611,13 +8623,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42418</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8644,7 +8656,7 @@
       <c r="I31" t="n">
         <v>1.51</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42418</v>
       </c>
       <c r="K31" t="n">
@@ -8657,13 +8669,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8690,7 +8702,7 @@
       <c r="I32" t="n">
         <v>1.51</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="K32" t="n">
@@ -8703,13 +8715,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8736,7 +8748,7 @@
       <c r="I33" t="n">
         <v>1.55</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="K33" t="n">
@@ -8749,13 +8761,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8782,7 +8794,7 @@
       <c r="I34" t="n">
         <v>1.53</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="K34" t="n">
@@ -8795,13 +8807,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8828,7 +8840,7 @@
       <c r="I35" t="n">
         <v>2.72</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K35" t="n">
@@ -8841,13 +8853,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8874,7 +8886,7 @@
       <c r="I36" t="n">
         <v>2.77</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="K36" t="n">
@@ -8887,13 +8899,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42937</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8920,7 +8932,7 @@
       <c r="I37" t="n">
         <v>2.69</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42937</v>
       </c>
       <c r="K37" t="n">
@@ -8933,13 +8945,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8966,7 +8978,7 @@
       <c r="I38" t="n">
         <v>2.59</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="K38" t="n">
@@ -8979,13 +8991,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9012,7 +9024,7 @@
       <c r="I39" t="n">
         <v>2.28</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="K39" t="n">
@@ -9025,13 +9037,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9058,7 +9070,7 @@
       <c r="I40" t="n">
         <v>2.36</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="K40" t="n">
@@ -9071,13 +9083,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9104,7 +9116,7 @@
       <c r="I41" t="n">
         <v>2.5</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="K41" t="n">
@@ -9117,13 +9129,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9150,7 +9162,7 @@
       <c r="I42" t="n">
         <v>2.42</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="K42" t="n">
@@ -9163,13 +9175,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9196,7 +9208,7 @@
       <c r="I43" t="n">
         <v>2.75</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="K43" t="n">
@@ -9209,13 +9221,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9242,7 +9254,7 @@
       <c r="I44" t="n">
         <v>2.68</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="K44" t="n">
@@ -9255,13 +9267,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9288,7 +9300,7 @@
       <c r="I45" t="n">
         <v>2.63</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="K45" t="n">
@@ -9301,13 +9313,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9334,7 +9346,7 @@
       <c r="I46" t="n">
         <v>2.7</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="K46" t="n">
@@ -9347,13 +9359,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9380,7 +9392,7 @@
       <c r="I47" t="n">
         <v>2.75</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="K47" t="n">
@@ -9393,13 +9405,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9426,7 +9438,7 @@
       <c r="I48" t="n">
         <v>2.93</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K48" t="n">
@@ -9439,13 +9451,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9472,7 +9484,7 @@
       <c r="I49" t="n">
         <v>2.99</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K49" t="n">
@@ -9485,13 +9497,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9518,7 +9530,7 @@
       <c r="I50" t="n">
         <v>3.13</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K50" t="n">
@@ -9531,13 +9543,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44245</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9564,7 +9576,7 @@
       <c r="I51" t="n">
         <v>3.13</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44245</v>
       </c>
       <c r="K51" t="n">
@@ -9577,13 +9589,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9610,7 +9622,7 @@
       <c r="I52" t="n">
         <v>3.1</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="K52" t="n">
@@ -9623,13 +9635,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9656,7 +9668,7 @@
       <c r="I53" t="n">
         <v>3.19</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="K53" t="n">
@@ -9669,13 +9681,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9702,7 +9714,7 @@
       <c r="I54" t="n">
         <v>3.13</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="K54" t="n">
@@ -9715,13 +9727,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9748,7 +9760,7 @@
       <c r="I55" t="n">
         <v>2.55</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="K55" t="n">
@@ -9761,13 +9773,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9794,7 +9806,7 @@
       <c r="I56" t="n">
         <v>2.41</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K56" t="n">
@@ -9807,13 +9819,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9840,7 +9852,7 @@
       <c r="I57" t="n">
         <v>2.3</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="K57" t="n">
@@ -9853,13 +9865,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9886,7 +9898,7 @@
       <c r="I58" t="n">
         <v>2.29</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="K58" t="n">
@@ -9899,13 +9911,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9932,7 +9944,7 @@
       <c r="I59" t="n">
         <v>2.13</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="K59" t="n">
@@ -9945,13 +9957,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9978,7 +9990,7 @@
       <c r="I60" t="n">
         <v>1.92</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="K60" t="n">
@@ -9991,13 +10003,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10024,7 +10036,7 @@
       <c r="I61" t="n">
         <v>1.8</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="K61" t="n">
@@ -10037,13 +10049,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10070,7 +10082,7 @@
       <c r="I62" t="n">
         <v>1.92</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="K62" t="n">
@@ -10083,13 +10095,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10116,7 +10128,7 @@
       <c r="I63" t="n">
         <v>2.77</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="K63" t="n">
@@ -10129,13 +10141,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10162,7 +10174,7 @@
       <c r="I64" t="n">
         <v>3.149999999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="K64" t="n">
@@ -10175,13 +10187,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10208,7 +10220,7 @@
       <c r="I65" t="n">
         <v>3.44</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="K65" t="n">
@@ -10221,13 +10233,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10254,7 +10266,7 @@
       <c r="I66" t="n">
         <v>3.48</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="K66" t="n">
@@ -10267,13 +10279,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10300,7 +10312,7 @@
       <c r="I67" t="n">
         <v>3.51</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="K67" t="n">
@@ -10313,13 +10325,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10346,7 +10358,7 @@
       <c r="I68" t="n">
         <v>3.529999999999999</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="K68" t="n">
@@ -10359,13 +10371,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10392,7 +10404,7 @@
       <c r="I69" t="n">
         <v>3.55</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="K69" t="n">
@@ -10405,13 +10417,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10438,7 +10450,7 @@
       <c r="I70" t="n">
         <v>3.56</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K70" t="n">
@@ -10451,13 +10463,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10484,7 +10496,7 @@
       <c r="I71" t="n">
         <v>2.63</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="K71" t="n">
@@ -10497,13 +10509,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10530,7 +10542,7 @@
       <c r="I72" t="n">
         <v>2.58</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K72" t="n">
@@ -10543,13 +10555,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10576,7 +10588,7 @@
       <c r="I73" t="n">
         <v>2.53</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K73" t="n">
@@ -10613,52 +10625,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40024</v>
       </c>
       <c r="C2" t="n">
@@ -10687,10 +10699,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="C3" t="n">
@@ -10719,10 +10731,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="C4" t="n">
@@ -10751,10 +10763,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40297</v>
       </c>
       <c r="C5" t="n">
@@ -10783,10 +10795,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40388</v>
       </c>
       <c r="C6" t="n">
@@ -10815,10 +10827,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40479</v>
       </c>
       <c r="C7" t="n">
@@ -10847,10 +10859,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40598</v>
       </c>
       <c r="C8" t="n">
@@ -10879,10 +10891,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40661</v>
       </c>
       <c r="C9" t="n">
@@ -10911,10 +10923,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="C10" t="n">
@@ -10943,10 +10955,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="C11" t="n">
@@ -10975,10 +10987,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="C12" t="n">
@@ -11007,10 +11019,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="C13" t="n">
@@ -11039,10 +11051,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="C14" t="n">
@@ -11071,10 +11083,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="C15" t="n">
@@ -11103,10 +11115,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="C16" t="n">
@@ -11135,10 +11147,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="C17" t="n">
@@ -11167,10 +11179,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="C18" t="n">
@@ -11199,10 +11211,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="C19" t="n">
@@ -11231,10 +11243,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41690</v>
       </c>
       <c r="C20" t="n">
@@ -11263,10 +11275,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="C21" t="n">
@@ -11295,10 +11307,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C22" t="n">
@@ -11327,10 +11339,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41936</v>
       </c>
       <c r="C23" t="n">
@@ -11359,10 +11371,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="C24" t="n">
@@ -11391,10 +11403,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="C25" t="n">
@@ -11423,10 +11435,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="C26" t="n">
@@ -11455,10 +11467,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C27" t="n">
@@ -11487,10 +11499,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42418</v>
       </c>
       <c r="C28" t="n">
@@ -11519,10 +11531,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="C29" t="n">
@@ -11551,10 +11563,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="C30" t="n">
@@ -11583,10 +11595,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="C31" t="n">
@@ -11615,10 +11627,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C32" t="n">
@@ -11647,10 +11659,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="C33" t="n">
@@ -11679,10 +11691,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42937</v>
       </c>
       <c r="C34" t="n">
@@ -11711,10 +11723,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="C35" t="n">
@@ -11743,10 +11755,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="C36" t="n">
@@ -11775,10 +11787,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="C37" t="n">
@@ -11807,10 +11819,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="C38" t="n">
@@ -11839,10 +11851,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="C39" t="n">
@@ -11871,10 +11883,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="C40" t="n">
@@ -11903,10 +11915,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="C41" t="n">
@@ -11935,10 +11947,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="C42" t="n">
@@ -11967,10 +11979,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="C43" t="n">
@@ -11999,10 +12011,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="C44" t="n">
@@ -12031,10 +12043,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C45" t="n">
@@ -12063,10 +12075,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C46" t="n">
@@ -12095,10 +12107,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C47" t="n">
@@ -12127,10 +12139,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44245</v>
       </c>
       <c r="C48" t="n">
@@ -12159,10 +12171,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="C49" t="n">
@@ -12191,10 +12203,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="C50" t="n">
@@ -12223,10 +12235,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="C51" t="n">
@@ -12255,10 +12267,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="C52" t="n">
@@ -12287,10 +12299,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C53" t="n">
@@ -12319,10 +12331,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="C54" t="n">
@@ -12351,10 +12363,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="C55" t="n">
@@ -12383,10 +12395,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="C56" t="n">
@@ -12415,10 +12427,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="C57" t="n">
@@ -12447,10 +12459,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="C58" t="n">
@@ -12479,10 +12491,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="C59" t="n">
@@ -12511,10 +12523,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="C60" t="n">
@@ -12543,10 +12555,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="C61" t="n">
@@ -12575,10 +12587,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="C62" t="n">
@@ -12607,10 +12619,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="C63" t="n">
@@ -12639,10 +12651,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="C64" t="n">
@@ -12671,10 +12683,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="C65" t="n">
@@ -12703,10 +12715,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C66" t="n">
@@ -12735,10 +12747,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C67" t="n">
@@ -12767,10 +12779,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="C68" t="n">
@@ -12799,10 +12811,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C69" t="n">
@@ -12831,10 +12843,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="C70" t="n">
@@ -12881,12 +12893,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/CL.xlsx
+++ b/salidas/empresas/CL.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>16.9949836730957</v>
+        <v>16.99497413635254</v>
       </c>
       <c r="C2" t="n">
         <v>27.44499969482422</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>16.8680305480957</v>
+        <v>16.86802673339844</v>
       </c>
       <c r="C3" t="n">
         <v>27.23999977111816</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>17.67924308776855</v>
+        <v>17.67923164367676</v>
       </c>
       <c r="C4" t="n">
         <v>28.54999923706055</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>18.40814018249512</v>
+        <v>18.40813255310059</v>
       </c>
       <c r="C5" t="n">
         <v>29.55999946594238</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>18.78801155090332</v>
+        <v>18.78800773620605</v>
       </c>
       <c r="C6" t="n">
         <v>30.17000007629395</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>18.6510124206543</v>
+        <v>18.65101432800293</v>
       </c>
       <c r="C7" t="n">
         <v>29.95000076293945</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>18.56612968444824</v>
+        <v>18.56612777709961</v>
       </c>
       <c r="C8" t="n">
         <v>29.65999984741211</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>18.73513221740723</v>
+        <v>18.73513984680176</v>
       </c>
       <c r="C9" t="n">
         <v>29.93000030517578</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>19.43621444702148</v>
+        <v>19.43622398376465</v>
       </c>
       <c r="C10" t="n">
         <v>31.04999923706055</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>20.12843704223633</v>
+        <v>20.12844467163086</v>
       </c>
       <c r="C11" t="n">
         <v>31.98500061035156</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>20.46826171875</v>
+        <v>20.46827125549316</v>
       </c>
       <c r="C12" t="n">
         <v>32.52500152587891</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>20.52805328369141</v>
+        <v>20.52804946899414</v>
       </c>
       <c r="C13" t="n">
         <v>32.61999893188477</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>21.59508514404297</v>
+        <v>21.59509086608887</v>
       </c>
       <c r="C14" t="n">
         <v>34.15000152587891</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>21.31369590759277</v>
+        <v>21.31369018554688</v>
       </c>
       <c r="C15" t="n">
         <v>33.70500183105469</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>21.11765289306641</v>
+        <v>21.11766052246094</v>
       </c>
       <c r="C16" t="n">
         <v>33.39500045776367</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>21.53374481201172</v>
+        <v>21.53373146057129</v>
       </c>
       <c r="C17" t="n">
         <v>33.86999893188477</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>21.2857837677002</v>
+        <v>21.28577995300293</v>
       </c>
       <c r="C18" t="n">
         <v>33.47999954223633</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>20.61503791809082</v>
+        <v>20.61503982543945</v>
       </c>
       <c r="C19" t="n">
         <v>32.42499923706055</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>21.09268188476562</v>
+        <v>21.09268760681152</v>
       </c>
       <c r="C20" t="n">
         <v>33</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>21.19496536254883</v>
+        <v>21.19494819641113</v>
       </c>
       <c r="C21" t="n">
         <v>33.15999984741211</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>22.79288673400879</v>
+        <v>22.79288864135742</v>
       </c>
       <c r="C22" t="n">
         <v>35.65999984741211</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>24.49529266357422</v>
+        <v>24.49529457092285</v>
       </c>
       <c r="C23" t="n">
         <v>38.1349983215332</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>25.71892738342285</v>
+        <v>25.71893692016602</v>
       </c>
       <c r="C24" t="n">
         <v>40.04000091552734</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>25.03805541992188</v>
+        <v>25.03806304931641</v>
       </c>
       <c r="C25" t="n">
         <v>38.97999954223633</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>24.68773460388184</v>
+        <v>24.6877326965332</v>
       </c>
       <c r="C26" t="n">
         <v>38.25</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>24.55542755126953</v>
+        <v>24.5554141998291</v>
       </c>
       <c r="C27" t="n">
         <v>38.04499816894531</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>25.14277648925781</v>
+        <v>25.14276695251465</v>
       </c>
       <c r="C28" t="n">
         <v>38.95500183105469</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>22.93441963195801</v>
+        <v>22.93442153930664</v>
       </c>
       <c r="C29" t="n">
         <v>35.34999847412109</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>24.12168312072754</v>
+        <v>24.12168502807617</v>
       </c>
       <c r="C30" t="n">
         <v>37.18000030517578</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>22.41539001464844</v>
+        <v>22.41539573669434</v>
       </c>
       <c r="C31" t="n">
         <v>34.54999923706055</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>24.23381233215332</v>
+        <v>24.23382377624512</v>
       </c>
       <c r="C32" t="n">
         <v>37.1349983215332</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>24.58620834350586</v>
+        <v>24.58621597290039</v>
       </c>
       <c r="C34" t="n">
         <v>37.67499923706055</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>20.60927963256836</v>
+        <v>20.60928535461426</v>
       </c>
       <c r="C35" t="n">
         <v>31.3799991607666</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>21.36785125732422</v>
+        <v>21.36784934997559</v>
       </c>
       <c r="C36" t="n">
         <v>32.53499984741211</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>22.50733757019043</v>
+        <v>22.50732803344727</v>
       </c>
       <c r="C37" t="n">
         <v>34.27000045776367</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>21.49353408813477</v>
+        <v>21.4935359954834</v>
       </c>
       <c r="C38" t="n">
         <v>32.52000045776367</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>19.88747024536133</v>
+        <v>19.88747215270996</v>
       </c>
       <c r="C39" t="n">
         <v>30.09000015258789</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>19.49091148376465</v>
+        <v>19.49090957641602</v>
       </c>
       <c r="C40" t="n">
         <v>29.48999977111816</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>19.6401195526123</v>
+        <v>19.64011764526367</v>
       </c>
       <c r="C41" t="n">
         <v>29.5</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>21.95366668701172</v>
+        <v>21.95365715026855</v>
       </c>
       <c r="C42" t="n">
         <v>32.97499847412109</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>23.54816627502441</v>
+        <v>23.54817390441895</v>
       </c>
       <c r="C43" t="n">
         <v>35.36999893188477</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>24.25870132446289</v>
+        <v>24.25870323181152</v>
       </c>
       <c r="C44" t="n">
         <v>36.22000122070312</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>24.34577560424805</v>
+        <v>24.34578323364258</v>
       </c>
       <c r="C45" t="n">
         <v>36.34999847412109</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>26.47924041748047</v>
+        <v>26.4792423248291</v>
       </c>
       <c r="C47" t="n">
         <v>39.31499862670898</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>28.35161781311035</v>
+        <v>28.35160255432129</v>
       </c>
       <c r="C48" t="n">
         <v>42.09500122070312</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>27.66463088989258</v>
+        <v>27.66463661193848</v>
       </c>
       <c r="C49" t="n">
         <v>41.07500076293945</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>27.10124015808105</v>
+        <v>27.10125732421875</v>
       </c>
       <c r="C50" t="n">
         <v>40.01499938964844</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>28.87232208251953</v>
+        <v>28.8723316192627</v>
       </c>
       <c r="C52" t="n">
         <v>42.63000106811523</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>28.65883445739746</v>
+        <v>28.65883636474609</v>
       </c>
       <c r="C53" t="n">
         <v>42.04999923706055</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>26.8391170501709</v>
+        <v>26.83911895751953</v>
       </c>
       <c r="C55" t="n">
         <v>39.38000106811523</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>27.08699035644531</v>
+        <v>27.08699226379395</v>
       </c>
       <c r="C56" t="n">
         <v>39.4900016784668</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>25.32416915893555</v>
+        <v>25.32417297363281</v>
       </c>
       <c r="C57" t="n">
         <v>36.91999816894531</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>26.35991477966309</v>
+        <v>26.35990524291992</v>
       </c>
       <c r="C58" t="n">
         <v>38.43000030517578</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>26.63196754455566</v>
+        <v>26.63196563720703</v>
       </c>
       <c r="C59" t="n">
         <v>38.56000137329102</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>26.43513298034668</v>
+        <v>26.43512725830078</v>
       </c>
       <c r="C60" t="n">
         <v>38.27500152587891</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>27.75429725646973</v>
+        <v>27.75430107116699</v>
       </c>
       <c r="C61" t="n">
         <v>40.18500137329102</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>26.69017791748047</v>
+        <v>26.69018173217773</v>
       </c>
       <c r="C62" t="n">
         <v>38.3849983215332</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>27.2985954284668</v>
+        <v>27.29860496520996</v>
       </c>
       <c r="C63" t="n">
         <v>39.2599983215332</v>
@@ -1800,7 +1800,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>28.07737731933594</v>
+        <v>28.07734680175781</v>
       </c>
       <c r="C64" t="n">
         <v>40.38000106811523</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>29.5362720489502</v>
+        <v>29.53627395629883</v>
       </c>
       <c r="C65" t="n">
         <v>42.17499923706055</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>30.6497859954834</v>
+        <v>30.64978790283203</v>
       </c>
       <c r="C66" t="n">
         <v>43.76499938964844</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>30.6077709197998</v>
+        <v>30.60776901245117</v>
       </c>
       <c r="C67" t="n">
         <v>43.70500183105469</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>29.74058151245117</v>
+        <v>29.74057960510254</v>
       </c>
       <c r="C68" t="n">
         <v>42.18999862670898</v>
@@ -1945,7 +1945,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>31.71083068847656</v>
+        <v>31.71085357666016</v>
       </c>
       <c r="C69" t="n">
         <v>44.98500061035156</v>
@@ -1974,7 +1974,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>31.25618934631348</v>
+        <v>31.25617790222168</v>
       </c>
       <c r="C70" t="n">
         <v>44.34000015258789</v>
@@ -2003,7 +2003,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>32.05474853515625</v>
+        <v>32.05474472045898</v>
       </c>
       <c r="C71" t="n">
         <v>45.18500137329102</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>32.45556259155273</v>
+        <v>32.45556640625</v>
       </c>
       <c r="C72" t="n">
         <v>45.75</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>32.77125930786133</v>
+        <v>32.7712516784668</v>
       </c>
       <c r="C73" t="n">
         <v>46.19499969482422</v>
@@ -2090,7 +2090,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>32.38769149780273</v>
+        <v>32.38770294189453</v>
       </c>
       <c r="C74" t="n">
         <v>45.36000061035156</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>33.26591873168945</v>
+        <v>33.26592254638672</v>
       </c>
       <c r="C75" t="n">
         <v>46.59000015258789</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>35.54675674438477</v>
+        <v>35.54676818847656</v>
       </c>
       <c r="C77" t="n">
         <v>49.47000122070312</v>
@@ -2206,7 +2206,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>35.31682205200195</v>
+        <v>35.31683349609375</v>
       </c>
       <c r="C78" t="n">
         <v>49.15000152587891</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>37.4006233215332</v>
+        <v>37.40064239501953</v>
       </c>
       <c r="C79" t="n">
         <v>52.04999923706055</v>
@@ -2293,7 +2293,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>38.42015838623047</v>
+        <v>38.4201545715332</v>
       </c>
       <c r="C81" t="n">
         <v>53.15499877929688</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>38.74902725219727</v>
+        <v>38.74903106689453</v>
       </c>
       <c r="C82" t="n">
         <v>53.61000061035156</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>39.4326286315918</v>
+        <v>39.43262481689453</v>
       </c>
       <c r="C84" t="n">
         <v>54.25</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>37.99341583251953</v>
+        <v>37.99343109130859</v>
       </c>
       <c r="C85" t="n">
         <v>52.27000045776367</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>39.24514770507812</v>
+        <v>39.24515914916992</v>
       </c>
       <c r="C86" t="n">
         <v>53.68500137329102</v>
@@ -2467,7 +2467,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>41.82567977905273</v>
+        <v>41.82567596435547</v>
       </c>
       <c r="C87" t="n">
         <v>57.21500015258789</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>43.14152908325195</v>
+        <v>43.14151763916016</v>
       </c>
       <c r="C88" t="n">
         <v>59.01499938964844</v>
@@ -2525,7 +2525,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>43.89768218994141</v>
+        <v>43.8976936340332</v>
       </c>
       <c r="C89" t="n">
         <v>59.70500183105469</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>42.52645874023438</v>
+        <v>42.52645492553711</v>
       </c>
       <c r="C90" t="n">
         <v>57.84000015258789</v>
@@ -2583,7 +2583,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>42.12207794189453</v>
+        <v>42.12207412719727</v>
       </c>
       <c r="C91" t="n">
         <v>57.29000091552734</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>44.27501678466797</v>
+        <v>44.27499771118164</v>
       </c>
       <c r="C92" t="n">
         <v>59.86999893188477</v>
@@ -2641,7 +2641,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>42.72201538085938</v>
+        <v>42.7220344543457</v>
       </c>
       <c r="C93" t="n">
         <v>57.77000045776367</v>
@@ -2699,7 +2699,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>48.12714004516602</v>
+        <v>48.12713623046875</v>
       </c>
       <c r="C95" t="n">
         <v>64.73000335693359</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>48.48401641845703</v>
+        <v>48.4840087890625</v>
       </c>
       <c r="C97" t="n">
         <v>65.20999908447266</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>45.76520919799805</v>
+        <v>45.76520156860352</v>
       </c>
       <c r="C98" t="n">
         <v>61.22999954223633</v>
@@ -2844,7 +2844,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>48.48585510253906</v>
+        <v>48.4858512878418</v>
       </c>
       <c r="C100" t="n">
         <v>64.87000274658203</v>
@@ -2873,7 +2873,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>50.57314682006836</v>
+        <v>50.5731315612793</v>
       </c>
       <c r="C101" t="n">
         <v>67.30000305175781</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>51.39973449707031</v>
+        <v>51.39971923828125</v>
       </c>
       <c r="C102" t="n">
         <v>68.40000152587891</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>51.23440170288086</v>
+        <v>51.23441696166992</v>
       </c>
       <c r="C103" t="n">
         <v>68.18000030517578</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>47.88993072509766</v>
+        <v>47.88992691040039</v>
       </c>
       <c r="C104" t="n">
         <v>63.40000152587891</v>
@@ -2989,7 +2989,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>48.89455413818359</v>
+        <v>48.89456558227539</v>
       </c>
       <c r="C105" t="n">
         <v>64.73000335693359</v>
@@ -3018,7 +3018,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>49.26469421386719</v>
+        <v>49.26468276977539</v>
       </c>
       <c r="C106" t="n">
         <v>65.22000122070312</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>50.80253601074219</v>
+        <v>50.80253219604492</v>
       </c>
       <c r="C107" t="n">
         <v>66.87999725341797</v>
@@ -3076,7 +3076,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>52.86106872558594</v>
+        <v>52.8610725402832</v>
       </c>
       <c r="C108" t="n">
         <v>69.58999633789062</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>52.55723190307617</v>
+        <v>52.55721664428711</v>
       </c>
       <c r="C109" t="n">
         <v>69.19000244140625</v>
@@ -3163,7 +3163,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>54.07770538330078</v>
+        <v>54.07768249511719</v>
       </c>
       <c r="C111" t="n">
         <v>70.81999969482422</v>
@@ -3192,7 +3192,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>52.94756698608398</v>
+        <v>52.94757080078125</v>
       </c>
       <c r="C112" t="n">
         <v>69.33999633789062</v>
@@ -3221,7 +3221,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>51.66133499145508</v>
+        <v>51.66133880615234</v>
       </c>
       <c r="C113" t="n">
         <v>67.27999877929688</v>
@@ -3250,7 +3250,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>51.28508377075195</v>
+        <v>51.28507614135742</v>
       </c>
       <c r="C114" t="n">
         <v>66.79000091552734</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>50.22544860839844</v>
+        <v>50.22543716430664</v>
       </c>
       <c r="C115" t="n">
         <v>65.41000366210938</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>52.52392196655273</v>
+        <v>52.5239372253418</v>
       </c>
       <c r="C116" t="n">
         <v>68.01999664306641</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>48.50086212158203</v>
+        <v>48.50084686279297</v>
       </c>
       <c r="C117" t="n">
         <v>62.81000137329102</v>
@@ -3366,7 +3366,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>49.00275802612305</v>
+        <v>49.00276565551758</v>
       </c>
       <c r="C118" t="n">
         <v>63.45999908447266</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>51.5263671875</v>
+        <v>51.52634811401367</v>
       </c>
       <c r="C119" t="n">
         <v>66.34999847412109</v>
@@ -3453,7 +3453,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>51.73603057861328</v>
+        <v>51.73603820800781</v>
       </c>
       <c r="C121" t="n">
         <v>66.62000274658203</v>
@@ -3511,7 +3511,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>51.28706359863281</v>
+        <v>51.28705596923828</v>
       </c>
       <c r="C123" t="n">
         <v>65.63999938964844</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>55.2015495300293</v>
+        <v>55.20156097412109</v>
       </c>
       <c r="C124" t="n">
         <v>70.65000152587891</v>
@@ -3569,7 +3569,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>55.71574401855469</v>
+        <v>55.71575927734375</v>
       </c>
       <c r="C125" t="n">
         <v>70.91999816894531</v>
@@ -3598,7 +3598,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>55.31508636474609</v>
+        <v>55.31509399414062</v>
       </c>
       <c r="C126" t="n">
         <v>70.41000366210938</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>57.5069465637207</v>
+        <v>57.50695419311523</v>
       </c>
       <c r="C127" t="n">
         <v>73.19999694824219</v>
@@ -3656,7 +3656,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>58.78071212768555</v>
+        <v>58.78073120117188</v>
       </c>
       <c r="C128" t="n">
         <v>74.43000030517578</v>
@@ -3685,7 +3685,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>58.70964431762695</v>
+        <v>58.70962524414062</v>
       </c>
       <c r="C129" t="n">
         <v>74.33999633789062</v>
@@ -3714,7 +3714,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>58.55168151855469</v>
+        <v>58.55168533325195</v>
       </c>
       <c r="C130" t="n">
         <v>74.13999938964844</v>
@@ -3743,7 +3743,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>56.66440200805664</v>
+        <v>56.6644172668457</v>
       </c>
       <c r="C131" t="n">
         <v>71.36000061035156</v>
@@ -3772,7 +3772,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>51.79680252075195</v>
+        <v>51.79680633544922</v>
       </c>
       <c r="C132" t="n">
         <v>65.23000335693359</v>
@@ -3830,7 +3830,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>51.57708740234375</v>
+        <v>51.57707595825195</v>
       </c>
       <c r="C134" t="n">
         <v>64.58000183105469</v>
@@ -3859,7 +3859,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>58.28577423095703</v>
+        <v>58.28575897216797</v>
       </c>
       <c r="C135" t="n">
         <v>72.98000335693359</v>
@@ -3888,7 +3888,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>58.4534912109375</v>
+        <v>58.45348358154297</v>
       </c>
       <c r="C136" t="n">
         <v>73.19000244140625</v>
@@ -3917,7 +3917,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>57.84616470336914</v>
+        <v>57.84617614746094</v>
       </c>
       <c r="C137" t="n">
         <v>72.04000091552734</v>
@@ -3946,7 +3946,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>61.31498718261719</v>
+        <v>61.31500625610352</v>
       </c>
       <c r="C138" t="n">
         <v>76.36000061035156</v>
@@ -4004,7 +4004,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>58.29747772216797</v>
+        <v>58.2974967956543</v>
       </c>
       <c r="C140" t="n">
         <v>72.19999694824219</v>
@@ -4033,7 +4033,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>57.84530639648438</v>
+        <v>57.84531021118164</v>
       </c>
       <c r="C141" t="n">
         <v>71.63999938964844</v>
@@ -4062,7 +4062,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>58.82230377197266</v>
+        <v>58.82234191894531</v>
       </c>
       <c r="C142" t="n">
         <v>72.84999847412109</v>
@@ -4091,7 +4091,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>57.19726943969727</v>
+        <v>57.19727325439453</v>
       </c>
       <c r="C143" t="n">
         <v>70.44999694824219</v>
@@ -4120,7 +4120,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>58.82101058959961</v>
+        <v>58.82103729248047</v>
       </c>
       <c r="C144" t="n">
         <v>72.44999694824219</v>
@@ -4149,7 +4149,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>61.25668334960938</v>
+        <v>61.25667572021484</v>
       </c>
       <c r="C145" t="n">
         <v>75.44999694824219</v>
@@ -4207,7 +4207,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>56.28620529174805</v>
+        <v>56.28618621826172</v>
       </c>
       <c r="C147" t="n">
         <v>68.97000122070312</v>
@@ -4236,7 +4236,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>58.4978141784668</v>
+        <v>58.49780654907227</v>
       </c>
       <c r="C148" t="n">
         <v>71.68000030517578</v>
@@ -4265,7 +4265,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>53.54598617553711</v>
+        <v>53.54599761962891</v>
       </c>
       <c r="C149" t="n">
         <v>65.23000335693359</v>
@@ -4294,7 +4294,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>51.789306640625</v>
+        <v>51.78931045532227</v>
       </c>
       <c r="C150" t="n">
         <v>63.09000015258789</v>
@@ -4323,7 +4323,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>53.20122146606445</v>
+        <v>53.20121765136719</v>
       </c>
       <c r="C151" t="n">
         <v>64.80999755859375</v>
@@ -4352,7 +4352,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>55.36150741577148</v>
+        <v>55.36150360107422</v>
       </c>
       <c r="C152" t="n">
         <v>67.01000213623047</v>
@@ -4410,7 +4410,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>55.31191253662109</v>
+        <v>55.31192779541016</v>
       </c>
       <c r="C154" t="n">
         <v>66.94999694824219</v>
@@ -4439,7 +4439,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>49.52559661865234</v>
+        <v>49.52560043334961</v>
       </c>
       <c r="C155" t="n">
         <v>59.54999923706055</v>
@@ -4468,7 +4468,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>52.82728958129883</v>
+        <v>52.82730865478516</v>
       </c>
       <c r="C156" t="n">
         <v>63.52000045776367</v>
@@ -4497,7 +4497,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>49.50064849853516</v>
+        <v>49.50064086914062</v>
       </c>
       <c r="C157" t="n">
         <v>59.52000045776367</v>
@@ -4526,7 +4526,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>54.15520858764648</v>
+        <v>54.15520095825195</v>
       </c>
       <c r="C158" t="n">
         <v>64.68000030517578</v>
@@ -4555,7 +4555,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>55.15156936645508</v>
+        <v>55.15157699584961</v>
       </c>
       <c r="C159" t="n">
         <v>65.87000274658203</v>
@@ -4584,7 +4584,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>57.3870964050293</v>
+        <v>57.38710021972656</v>
       </c>
       <c r="C160" t="n">
         <v>68.54000091552734</v>
@@ -4642,7 +4642,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>58.65668106079102</v>
+        <v>58.65670776367188</v>
       </c>
       <c r="C162" t="n">
         <v>69.62000274658203</v>
@@ -4671,7 +4671,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>60.38385009765625</v>
+        <v>60.38385772705078</v>
       </c>
       <c r="C163" t="n">
         <v>71.66999816894531</v>
@@ -4729,7 +4729,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>62.83601760864258</v>
+        <v>62.83600997924805</v>
       </c>
       <c r="C165" t="n">
         <v>74.15000152587891</v>
@@ -4758,7 +4758,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>62.29368591308594</v>
+        <v>62.29367065429688</v>
       </c>
       <c r="C166" t="n">
         <v>73.51000213623047</v>
@@ -4787,7 +4787,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>58.50115203857422</v>
+        <v>58.50113677978516</v>
       </c>
       <c r="C167" t="n">
         <v>68.59999847412109</v>
@@ -4816,7 +4816,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>57.83597564697266</v>
+        <v>57.83597946166992</v>
       </c>
       <c r="C168" t="n">
         <v>67.81999969482422</v>
@@ -4845,7 +4845,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>58.7058219909668</v>
+        <v>58.70581436157227</v>
       </c>
       <c r="C169" t="n">
         <v>68.83999633789062</v>
@@ -4874,7 +4874,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>63.30039978027344</v>
+        <v>63.30038833618164</v>
       </c>
       <c r="C170" t="n">
         <v>73.77999877929688</v>
@@ -4903,7 +4903,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>57.97245788574219</v>
+        <v>57.97246551513672</v>
       </c>
       <c r="C171" t="n">
         <v>67.56999969482422</v>
@@ -4932,7 +4932,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>56.93431091308594</v>
+        <v>56.93432998657227</v>
       </c>
       <c r="C172" t="n">
         <v>66.36000061035156</v>
@@ -4990,7 +4990,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>62.4334831237793</v>
+        <v>62.43349075317383</v>
       </c>
       <c r="C174" t="n">
         <v>72.33000183105469</v>
@@ -5077,7 +5077,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>68.81914520263672</v>
+        <v>68.81915283203125</v>
       </c>
       <c r="C177" t="n">
         <v>79.26000213623047</v>
@@ -5106,7 +5106,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>66.98709106445312</v>
+        <v>66.98709869384766</v>
       </c>
       <c r="C178" t="n">
         <v>77.15000152587891</v>
@@ -5164,7 +5164,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>74.76891326904297</v>
+        <v>74.7689208984375</v>
       </c>
       <c r="C180" t="n">
         <v>85.63999938964844</v>
@@ -5193,7 +5193,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>74.65543365478516</v>
+        <v>74.65542602539062</v>
       </c>
       <c r="C181" t="n">
         <v>85.51000213623047</v>
@@ -5280,7 +5280,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>69.20747375488281</v>
+        <v>69.20746612548828</v>
       </c>
       <c r="C184" t="n">
         <v>78.83000183105469</v>
@@ -5309,7 +5309,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>71.24813842773438</v>
+        <v>71.24813079833984</v>
       </c>
       <c r="C185" t="n">
         <v>80.69999694824219</v>
@@ -5367,7 +5367,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>71.82199859619141</v>
+        <v>71.82200622558594</v>
       </c>
       <c r="C187" t="n">
         <v>81.34999847412109</v>
@@ -5396,7 +5396,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>70.56684875488281</v>
+        <v>70.56684112548828</v>
       </c>
       <c r="C188" t="n">
         <v>79.5</v>
@@ -5425,7 +5425,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>69.19100952148438</v>
+        <v>69.19102478027344</v>
       </c>
       <c r="C189" t="n">
         <v>77.94999694824219</v>
@@ -5454,7 +5454,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>67.08733367919922</v>
+        <v>67.08734130859375</v>
       </c>
       <c r="C190" t="n">
         <v>75.58000183105469</v>
@@ -5570,7 +5570,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>74.02838897705078</v>
+        <v>74.02839660644531</v>
       </c>
       <c r="C194" t="n">
         <v>82.44999694824219</v>
@@ -5599,7 +5599,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>69.09018707275391</v>
+        <v>69.09017944335938</v>
       </c>
       <c r="C195" t="n">
         <v>76.94999694824219</v>
@@ -5628,7 +5628,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>68.08458709716797</v>
+        <v>68.08457183837891</v>
       </c>
       <c r="C196" t="n">
         <v>75.83000183105469</v>
@@ -5686,7 +5686,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>71.17517852783203</v>
+        <v>71.17518615722656</v>
       </c>
       <c r="C198" t="n">
         <v>78.80999755859375</v>
@@ -5744,7 +5744,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>71.54568481445312</v>
+        <v>71.54569244384766</v>
       </c>
       <c r="C200" t="n">
         <v>78.73999786376953</v>
@@ -5773,7 +5773,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>71.06409454345703</v>
+        <v>71.06410217285156</v>
       </c>
       <c r="C201" t="n">
         <v>78.20999908447266</v>
@@ -5802,7 +5802,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>63.83140563964844</v>
+        <v>63.83140182495117</v>
       </c>
       <c r="C202" t="n">
         <v>70.25</v>
@@ -5831,7 +5831,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>67.53578186035156</v>
+        <v>67.53577423095703</v>
       </c>
       <c r="C203" t="n">
         <v>73.83999633789062</v>
@@ -5860,7 +5860,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>70.86501312255859</v>
+        <v>70.86502075195312</v>
       </c>
       <c r="C204" t="n">
         <v>77.48000335693359</v>
@@ -5889,7 +5889,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>72.06317901611328</v>
+        <v>72.06317138671875</v>
       </c>
       <c r="C205" t="n">
         <v>78.79000091552734</v>
@@ -5918,7 +5918,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>68.59559631347656</v>
+        <v>68.5955810546875</v>
       </c>
       <c r="C206" t="n">
         <v>74.52999877929688</v>
@@ -5976,7 +5976,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>69.16623687744141</v>
+        <v>69.16625213623047</v>
       </c>
       <c r="C208" t="n">
         <v>75.15000152587891</v>
@@ -6034,7 +6034,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>68.89501953125</v>
+        <v>68.89502716064453</v>
       </c>
       <c r="C210" t="n">
         <v>74.37999725341797</v>
@@ -6121,7 +6121,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>68.48226928710938</v>
+        <v>68.48227691650391</v>
       </c>
       <c r="C213" t="n">
         <v>73.47000122070312</v>
@@ -6150,7 +6150,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>66.28249359130859</v>
+        <v>66.28250885009766</v>
       </c>
       <c r="C214" t="n">
         <v>71.11000061035156</v>
@@ -6179,7 +6179,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>70.48251342773438</v>
+        <v>70.48250579833984</v>
       </c>
       <c r="C215" t="n">
         <v>75.12000274658203</v>
@@ -6208,7 +6208,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>73.90716552734375</v>
+        <v>73.90717315673828</v>
       </c>
       <c r="C216" t="n">
         <v>78.76999664306641</v>
@@ -6237,7 +6237,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>74.78914642333984</v>
+        <v>74.78913879394531</v>
       </c>
       <c r="C217" t="n">
         <v>79.70999908447266</v>
@@ -6324,7 +6324,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>84.99556732177734</v>
+        <v>84.99555969238281</v>
       </c>
       <c r="C220" t="n">
         <v>90.05000305175781</v>
@@ -6411,7 +6411,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>92.12442779541016</v>
+        <v>92.12443542480469</v>
       </c>
       <c r="C223" t="n">
         <v>97.04000091552734</v>
@@ -6469,7 +6469,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>101.6210250854492</v>
+        <v>101.6210327148438</v>
       </c>
       <c r="C225" t="n">
         <v>106.5</v>
@@ -6527,7 +6527,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>89.86392211914062</v>
+        <v>89.86390686035156</v>
       </c>
       <c r="C227" t="n">
         <v>93.70999908447266</v>
@@ -6556,7 +6556,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>92.66405487060547</v>
+        <v>92.6640625</v>
       </c>
       <c r="C228" t="n">
         <v>96.62999725341797</v>
@@ -6585,7 +6585,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>87.17881774902344</v>
+        <v>87.1788330078125</v>
       </c>
       <c r="C229" t="n">
         <v>90.91000366210938</v>
@@ -6614,7 +6614,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>83.61299133300781</v>
+        <v>83.61299896240234</v>
       </c>
       <c r="C230" t="n">
         <v>86.69999694824219</v>
@@ -6643,7 +6643,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>87.923828125</v>
+        <v>87.92384338378906</v>
       </c>
       <c r="C231" t="n">
         <v>91.16999816894531</v>
@@ -6672,7 +6672,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>90.36374664306641</v>
+        <v>90.36375427246094</v>
       </c>
       <c r="C232" t="n">
         <v>93.69999694824219</v>
@@ -6701,7 +6701,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>89.40479278564453</v>
+        <v>89.40478515625</v>
       </c>
       <c r="C233" t="n">
         <v>92.19000244140625</v>
@@ -6730,7 +6730,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>90.13213348388672</v>
+        <v>90.13214111328125</v>
       </c>
       <c r="C234" t="n">
         <v>92.94000244140625</v>
@@ -6759,7 +6759,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>88.15376281738281</v>
+        <v>88.15377044677734</v>
       </c>
       <c r="C235" t="n">
         <v>90.90000152587891</v>
@@ -6846,7 +6846,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>77.98976135253906</v>
+        <v>77.98974609375</v>
       </c>
       <c r="C238" t="n">
         <v>79.94000244140625</v>
@@ -6875,7 +6875,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>75.67424011230469</v>
+        <v>75.67423248291016</v>
       </c>
       <c r="C239" t="n">
         <v>77.05000305175781</v>
@@ -6904,7 +6904,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>78.95460510253906</v>
+        <v>78.95459747314453</v>
       </c>
       <c r="C240" t="n">
         <v>80.38999938964844</v>
@@ -6933,7 +6933,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>77.60906219482422</v>
+        <v>77.60905456542969</v>
       </c>
       <c r="C241" t="n">
         <v>79.01999664306641</v>
@@ -6991,7 +6991,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>97.96604156494141</v>
+        <v>97.96604919433594</v>
       </c>
       <c r="C243" t="n">
         <v>99.13999938964844</v>
